--- a/data/processed_data/Video_063_CTRL1_5V/serie_temporal.xlsx
+++ b/data/processed_data/Video_063_CTRL1_5V/serie_temporal.xlsx
@@ -79817,7 +79817,7 @@
         <v>61.71</v>
       </c>
       <c r="M1845" s="2" t="n">
-        <v>282.1430252202197</v>
+        <v>282.1430252202196</v>
       </c>
     </row>
     <row r="1846">
@@ -79860,7 +79860,7 @@
         <v>61.74166666666667</v>
       </c>
       <c r="M1846" s="2" t="n">
-        <v>282.1496794120806</v>
+        <v>282.1496794120805</v>
       </c>
     </row>
     <row r="1847">
@@ -79903,7 +79903,7 @@
         <v>61.77666666666667</v>
       </c>
       <c r="M1847" s="2" t="n">
-        <v>282.1703325172395</v>
+        <v>282.1703325172394</v>
       </c>
     </row>
     <row r="1848">
@@ -79989,7 +79989,7 @@
         <v>61.84166666666667</v>
       </c>
       <c r="M1849" s="2" t="n">
-        <v>282.2713406025521</v>
+        <v>282.2713406025522</v>
       </c>
     </row>
   </sheetData>
@@ -80004,7 +80004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -80405,6 +80405,36 @@
         <v>0.4309</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>error de modelo borde sup (px)</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1.519</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>error de modelo borde inf (px)</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0.4525</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>error de modelo peor / grosor (%)</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0.538</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
